--- a/output/graficos_regionales/plot_regional_serie_i_ingr_m_2018_o_higgins.xlsx
+++ b/output/graficos_regionales/plot_regional_serie_i_ingr_m_2018_o_higgins.xlsx
@@ -288,7 +288,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-28 16:37</t>
+    <t xml:space="preserve">2026-10-05 01:57</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -726,7 +726,7 @@
         <v>683637.31</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>804762.62</v>
+        <v>804762.63</v>
       </c>
     </row>
     <row r="5">
@@ -737,7 +737,7 @@
         <v>672339.69</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>799364.12</v>
+        <v>799364.13</v>
       </c>
     </row>
     <row r="6">
@@ -811,7 +811,7 @@
         <v>13</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>682590.12</v>
+        <v>682590.13</v>
       </c>
       <c r="C12" s="2" t="n">
         <v>816660.56</v>
@@ -822,7 +822,7 @@
         <v>14</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>729410.62</v>
+        <v>729410.63</v>
       </c>
       <c r="C13" s="2" t="n">
         <v>876986.31</v>
@@ -833,10 +833,10 @@
         <v>15</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>691155.62</v>
+        <v>691155.63</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>826816.62</v>
+        <v>826816.63</v>
       </c>
     </row>
     <row r="15">
@@ -855,7 +855,7 @@
         <v>17</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>718980.12</v>
+        <v>718980.13</v>
       </c>
       <c r="C16" s="2" t="n">
         <v>844828.88</v>
@@ -913,7 +913,7 @@
         <v>722756.38</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>849932.62</v>
+        <v>849932.63</v>
       </c>
     </row>
     <row r="22">
@@ -943,7 +943,7 @@
         <v>25</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>721595.62</v>
+        <v>721595.63</v>
       </c>
       <c r="C24" s="2" t="n">
         <v>864071.75</v>
@@ -1001,7 +1001,7 @@
         <v>754506.88</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>885489.12</v>
+        <v>885489.13</v>
       </c>
     </row>
     <row r="30">
@@ -1012,7 +1012,7 @@
         <v>765508.06</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>873830.12</v>
+        <v>873830.13</v>
       </c>
     </row>
     <row r="31">
@@ -1075,7 +1075,7 @@
         <v>37</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>754252.12</v>
+        <v>754252.13</v>
       </c>
       <c r="C36" s="2" t="n">
         <v>900212.25</v>
@@ -1097,7 +1097,7 @@
         <v>39</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>771412.62</v>
+        <v>771412.63</v>
       </c>
       <c r="C38" s="2" t="n">
         <v>917146.44</v>
@@ -1130,7 +1130,7 @@
         <v>42</v>
       </c>
       <c r="B41" s="2" t="n">
-        <v>798539.62</v>
+        <v>798539.63</v>
       </c>
       <c r="C41" s="2" t="n">
         <v>928672.94</v>
@@ -1166,7 +1166,7 @@
         <v>827217.31</v>
       </c>
       <c r="C44" s="2" t="n">
-        <v>953641.12</v>
+        <v>953641.13</v>
       </c>
     </row>
     <row r="45">
@@ -1287,7 +1287,7 @@
         <v>904832.88</v>
       </c>
       <c r="C55" s="2" t="n">
-        <v>1048559.62</v>
+        <v>1048559.63</v>
       </c>
     </row>
     <row r="56">
@@ -1298,7 +1298,7 @@
         <v>916564.81</v>
       </c>
       <c r="C56" s="2" t="n">
-        <v>1059287.62</v>
+        <v>1059287.63</v>
       </c>
     </row>
     <row r="57">
@@ -1306,7 +1306,7 @@
         <v>58</v>
       </c>
       <c r="B57" s="2" t="n">
-        <v>928199.62</v>
+        <v>928199.63</v>
       </c>
       <c r="C57" s="2" t="n">
         <v>1074313.38</v>
@@ -1328,7 +1328,7 @@
         <v>60</v>
       </c>
       <c r="B59" s="2" t="n">
-        <v>933100.12</v>
+        <v>933100.13</v>
       </c>
       <c r="C59" s="2" t="n">
         <v>1086115.25</v>
@@ -1342,7 +1342,7 @@
         <v>925987.19</v>
       </c>
       <c r="C60" s="2" t="n">
-        <v>1093564.62</v>
+        <v>1093564.63</v>
       </c>
     </row>
     <row r="61">
@@ -1364,7 +1364,7 @@
         <v>978534.56</v>
       </c>
       <c r="C62" s="2" t="n">
-        <v>1145616.62</v>
+        <v>1145616.63</v>
       </c>
     </row>
     <row r="63">
@@ -1372,7 +1372,7 @@
         <v>64</v>
       </c>
       <c r="B63" s="2" t="n">
-        <v>965881.62</v>
+        <v>965881.63</v>
       </c>
       <c r="C63" s="2" t="n">
         <v>1133168.75</v>
@@ -1419,7 +1419,7 @@
         <v>1031511.25</v>
       </c>
       <c r="C67" s="2" t="n">
-        <v>1184430.62</v>
+        <v>1184430.63</v>
       </c>
     </row>
     <row r="68">
@@ -1471,7 +1471,7 @@
         <v>73</v>
       </c>
       <c r="B72" s="2" t="n">
-        <v>1045695.62</v>
+        <v>1045695.63</v>
       </c>
       <c r="C72" s="2" t="n">
         <v>1219650.75</v>
@@ -1515,10 +1515,10 @@
         <v>77</v>
       </c>
       <c r="B76" s="2" t="n">
-        <v>1071934.12</v>
+        <v>1071934.13</v>
       </c>
       <c r="C76" s="2" t="n">
-        <v>1240434.12</v>
+        <v>1240434.13</v>
       </c>
     </row>
     <row r="77">
@@ -1548,10 +1548,10 @@
         <v>80</v>
       </c>
       <c r="B79" s="2" t="n">
-        <v>1090626.12</v>
+        <v>1090626.13</v>
       </c>
       <c r="C79" s="2" t="n">
-        <v>1253268.12</v>
+        <v>1253268.13</v>
       </c>
     </row>
     <row r="80">
@@ -1559,10 +1559,10 @@
         <v>81</v>
       </c>
       <c r="B80" s="2" t="n">
-        <v>1112229.12</v>
+        <v>1112229.13</v>
       </c>
       <c r="C80" s="2" t="n">
-        <v>1274861.62</v>
+        <v>1274861.63</v>
       </c>
     </row>
     <row r="81">
@@ -1581,10 +1581,10 @@
         <v>83</v>
       </c>
       <c r="B82" s="2" t="n">
-        <v>1167582.12</v>
+        <v>1167582.13</v>
       </c>
       <c r="C82" s="2" t="n">
-        <v>1327655.12</v>
+        <v>1327655.13</v>
       </c>
     </row>
     <row r="83">
@@ -1614,7 +1614,7 @@
         <v>86</v>
       </c>
       <c r="B85" s="2" t="n">
-        <v>1161718.12</v>
+        <v>1161718.13</v>
       </c>
       <c r="C85" s="2" t="n">
         <v>1353554.88</v>
